--- a/testCasesZ.xlsx
+++ b/testCasesZ.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065A875E-431E-2B49-A38D-83E7794C84C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B449C04-6AC9-DE43-B670-BD7C19C6F770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="680" windowWidth="29400" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCaseTemplate" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -114,9 +114,6 @@
     <t>System is initialized and movie purchase is valid.</t>
   </si>
   <si>
-    <t>1. Call generateCode() function.               2. Observe return value.</t>
-  </si>
-  <si>
     <t>Function returns a unique integer code.</t>
   </si>
   <si>
@@ -124,6 +121,36 @@
   </si>
   <si>
     <t>Fail</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>1. Call generateCode() function.                                                  2. Observe return value.</t>
+  </si>
+  <si>
+    <t>GuestPurchaseTicket_1</t>
+  </si>
+  <si>
+    <t>Full System Inegration</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Verify that a guest user can successfully find a movie, pay via credit card, and receive a confirmation receipt</t>
+  </si>
+  <si>
+    <t>Database is connected showing movies and times.  Payment gateway is in test mode.</t>
+  </si>
+  <si>
+    <t>1. Navigate Movie Selection Page and select a film                                                                                     2. Proceed to payment page and enter valid credit card info.                                         3. Click "Confirm Purchase"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment Gateway apporves transcaction.                 Confirmation page displays receipt and generates a ticket.                </t>
+  </si>
+  <si>
+    <t>Transaction completed, Receipt and ticket generated and sent to user.</t>
   </si>
 </sst>
 </file>
@@ -542,11 +569,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" customWidth="1"/>
     <col min="5" max="5" width="26.5" customWidth="1"/>
@@ -616,7 +642,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>15</v>
@@ -651,7 +677,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>15</v>
@@ -698,18 +724,53 @@
         <v>30</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="K5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="91" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>13</v>
       </c>
     </row>

--- a/testCasesZ.xlsx
+++ b/testCasesZ.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B449C04-6AC9-DE43-B670-BD7C19C6F770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2880F734-F46A-4639-80B4-F670BB929EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCaseTemplate" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="83">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>Integration</t>
   </si>
   <si>
     <t>MovieSearch_1</t>
@@ -151,6 +148,126 @@
   </si>
   <si>
     <t>Transaction completed, Receipt and ticket generated and sent to user.</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Delux_Seat_Purchase</t>
+  </si>
+  <si>
+    <t>Database is connected showing movies and seats.  Payment gateway is in test mode.</t>
+  </si>
+  <si>
+    <t>1. Navigate Movie Selection Page and select a film                                                                                     2. Proceed to payment page and select a Delux upgrade.                                        3. Enter card info and click "Confirm Purchase"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment Gateway apporves transcaction.                 Confirmation of a delux reservation is noted and customer recieves a delux ticket         </t>
+  </si>
+  <si>
+    <t>Transaction completed, Receipt and delux ticket generated and sent to user. Delux status successfully reflected in seat database.</t>
+  </si>
+  <si>
+    <t>Verify that the delux seat upgrade functionality works as intended (In-Person Kiosk Version)</t>
+  </si>
+  <si>
+    <t>Verify that the delux seat upgrade functionality works as intended (Web browser version)</t>
+  </si>
+  <si>
+    <t>DeluxTicketWeb</t>
+  </si>
+  <si>
+    <t>DeluxTicketKiosk</t>
+  </si>
+  <si>
+    <t>GuestLogin</t>
+  </si>
+  <si>
+    <t>Verify that a guest user can successfully log in to the theater website</t>
+  </si>
+  <si>
+    <t>Database is connected and can access usernames and passwords for guest accounts. Test guest account is set up.</t>
+  </si>
+  <si>
+    <t>1. Navigate to theater website                                                                                     2. Click the "Sign Up/Log In" button                                         3. Enter credentials and sign in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confiration of user sign-in appears with correct credentials entered.             </t>
+  </si>
+  <si>
+    <t>Transaction completed, Receipt and delux ticket generated and sent to user. Delux status was not successfully reflected in seat database however.</t>
+  </si>
+  <si>
+    <t>User signed in successfully and received confirmation.</t>
+  </si>
+  <si>
+    <t>EmployeeLogin</t>
+  </si>
+  <si>
+    <t>Guest_Login_Page</t>
+  </si>
+  <si>
+    <t>Employee_Login_Page</t>
+  </si>
+  <si>
+    <t>Verify that an employee can successfully log in to the theater's employee website</t>
+  </si>
+  <si>
+    <t>Database is connected and can access usernames and passwords for employee  accounts. Test employee account is set up.</t>
+  </si>
+  <si>
+    <t>1. Navigate to employee portal site                                                                                    2. Navigate to employee theater site                                         3. Enter credentials and sign in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmation of sign-in and redirection to employee console.            </t>
+  </si>
+  <si>
+    <t>User signed in successfully and was redirected.</t>
+  </si>
+  <si>
+    <t>Employee_Console_Page</t>
+  </si>
+  <si>
+    <t>Verify that an employee can successfully edit movie times/names.</t>
+  </si>
+  <si>
+    <t>Database is connected and can access movie data. Test employee account is set up.</t>
+  </si>
+  <si>
+    <t>1. Navigate to employee theater site                                                                                    2. Sign in/wait for redirect                                       3. Attempt to edit a movie's viewing time and name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmation of changes and reflection on user site.            </t>
+  </si>
+  <si>
+    <t>Movie times/names successfully changed with changes reflected on the user site.</t>
+  </si>
+  <si>
+    <t>EmployeeInterface</t>
+  </si>
+  <si>
+    <t>TicketScannerTest</t>
+  </si>
+  <si>
+    <t>Ticket_Scanner</t>
+  </si>
+  <si>
+    <t>Verify that tickets will not scan more than once.</t>
+  </si>
+  <si>
+    <t>Ticket database is connected and can access unique ticket date. Test ticket is issued.</t>
+  </si>
+  <si>
+    <t>1. Print/generate code for ticket                                                                                    2. Scan at front gate                                       3. Observe results for repeated scans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket is voided when scanned for a second time.            </t>
+  </si>
+  <si>
+    <t>Ticket approved twice - only voided on the third scan.</t>
   </si>
 </sst>
 </file>
@@ -244,9 +361,6 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -264,6 +378,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -569,37 +686,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5" customWidth="1"/>
+    <col min="1" max="2" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.44140625" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="26.5" customWidth="1"/>
+    <col min="5" max="5" width="26.44140625" customWidth="1"/>
     <col min="6" max="6" width="16.33203125" customWidth="1"/>
-    <col min="7" max="7" width="34.5" customWidth="1"/>
+    <col min="7" max="7" width="34.44140625" customWidth="1"/>
     <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1640625" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" customWidth="1"/>
     <col min="10" max="10" width="9.33203125" customWidth="1"/>
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
+    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -634,143 +751,353 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="7" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:11" s="6" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="6" t="s">
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="102.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K6" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="78" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="6" t="s">
+    <row r="7" spans="1:11" ht="125.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="39" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="8" spans="1:11" ht="125.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="91.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="102.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="57" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="91" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" s="3" t="s">
+      <c r="K12" s="2" t="s">
         <v>13</v>
       </c>
     </row>

--- a/testCasesZ.xlsx
+++ b/testCasesZ.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2880F734-F46A-4639-80B4-F670BB929EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4125DF-E1BC-4207-AEAF-C7C37DAB0173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="87">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -156,36 +156,9 @@
     <t>P2</t>
   </si>
   <si>
-    <t>Delux_Seat_Purchase</t>
-  </si>
-  <si>
     <t>Database is connected showing movies and seats.  Payment gateway is in test mode.</t>
   </si>
   <si>
-    <t>1. Navigate Movie Selection Page and select a film                                                                                     2. Proceed to payment page and select a Delux upgrade.                                        3. Enter card info and click "Confirm Purchase"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payment Gateway apporves transcaction.                 Confirmation of a delux reservation is noted and customer recieves a delux ticket         </t>
-  </si>
-  <si>
-    <t>Transaction completed, Receipt and delux ticket generated and sent to user. Delux status successfully reflected in seat database.</t>
-  </si>
-  <si>
-    <t>Verify that the delux seat upgrade functionality works as intended (In-Person Kiosk Version)</t>
-  </si>
-  <si>
-    <t>Verify that the delux seat upgrade functionality works as intended (Web browser version)</t>
-  </si>
-  <si>
-    <t>DeluxTicketWeb</t>
-  </si>
-  <si>
-    <t>DeluxTicketKiosk</t>
-  </si>
-  <si>
-    <t>GuestLogin</t>
-  </si>
-  <si>
     <t>Verify that a guest user can successfully log in to the theater website</t>
   </si>
   <si>
@@ -198,21 +171,9 @@
     <t xml:space="preserve">Confiration of user sign-in appears with correct credentials entered.             </t>
   </si>
   <si>
-    <t>Transaction completed, Receipt and delux ticket generated and sent to user. Delux status was not successfully reflected in seat database however.</t>
-  </si>
-  <si>
     <t>User signed in successfully and received confirmation.</t>
   </si>
   <si>
-    <t>EmployeeLogin</t>
-  </si>
-  <si>
-    <t>Guest_Login_Page</t>
-  </si>
-  <si>
-    <t>Employee_Login_Page</t>
-  </si>
-  <si>
     <t>Verify that an employee can successfully log in to the theater's employee website</t>
   </si>
   <si>
@@ -228,31 +189,16 @@
     <t>User signed in successfully and was redirected.</t>
   </si>
   <si>
-    <t>Employee_Console_Page</t>
-  </si>
-  <si>
-    <t>Verify that an employee can successfully edit movie times/names.</t>
-  </si>
-  <si>
     <t>Database is connected and can access movie data. Test employee account is set up.</t>
   </si>
   <si>
-    <t>1. Navigate to employee theater site                                                                                    2. Sign in/wait for redirect                                       3. Attempt to edit a movie's viewing time and name.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Confirmation of changes and reflection on user site.            </t>
   </si>
   <si>
     <t>Movie times/names successfully changed with changes reflected on the user site.</t>
   </si>
   <si>
-    <t>EmployeeInterface</t>
-  </si>
-  <si>
-    <t>TicketScannerTest</t>
-  </si>
-  <si>
-    <t>Ticket_Scanner</t>
+    <t>EmployeeInterface_1</t>
   </si>
   <si>
     <t>Verify that tickets will not scan more than once.</t>
@@ -268,6 +214,75 @@
   </si>
   <si>
     <t>Ticket approved twice - only voided on the third scan.</t>
+  </si>
+  <si>
+    <t>isScanned
+validate(ticketID)</t>
+  </si>
+  <si>
+    <t>GuestLogin_1</t>
+  </si>
+  <si>
+    <t>EmployeeLogin_1</t>
+  </si>
+  <si>
+    <t>TicketScannerTest_1</t>
+  </si>
+  <si>
+    <t>EmployeePortal
+logIn()</t>
+  </si>
+  <si>
+    <t>UserPortal
+logIn()</t>
+  </si>
+  <si>
+    <t>DeluxeTicketKiosk_1</t>
+  </si>
+  <si>
+    <t>DeluxeTicketWeb_1</t>
+  </si>
+  <si>
+    <t>Verify that the deluxe seat upgrade functionality works as intended (Web browser version)</t>
+  </si>
+  <si>
+    <t>Verify that the deluxe seat upgrade functionality works as intended (In-Person Kiosk Version)</t>
+  </si>
+  <si>
+    <t>1. Navigate Movie Selection Page and select a film                                                                                     2. Proceed to payment page and select a deluxe upgrade.                                        3. Enter card info and click "Confirm Purchase"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment Gateway apporves transcaction.                 Confirmation of a deluxe reservation is noted and customer recieves a deluxe ticket         </t>
+  </si>
+  <si>
+    <t>Transaction completed, Receipt and deluxe ticket generated and sent to user. deluxe status was not successfully reflected in seat database however.</t>
+  </si>
+  <si>
+    <t>Transaction completed, Receipt and deluxe ticket generated and sent to user. deluxe status successfully reflected in seat database.</t>
+  </si>
+  <si>
+    <t>isDeluxe</t>
+  </si>
+  <si>
+    <t>updateTime()</t>
+  </si>
+  <si>
+    <t>Verify that an employee can successfully edit movie times.</t>
+  </si>
+  <si>
+    <t>Verify that an employee can successfully edit movie names.</t>
+  </si>
+  <si>
+    <t>1. Navigate to employee theater site                                                                                    2. Sign in/wait for redirect                                       3. Attempt to edit a movie's name.</t>
+  </si>
+  <si>
+    <t>1. Navigate to employee theater site                                                                                    2. Sign in/wait for redirect                                       3. Attempt to edit a movie's viewing time.</t>
+  </si>
+  <si>
+    <t>updateMovies()</t>
+  </si>
+  <si>
+    <t>EmployeeInterface_2</t>
   </si>
 </sst>
 </file>
@@ -686,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.109375" bestFit="1" customWidth="1"/>
@@ -893,31 +908,31 @@
     </row>
     <row r="7" spans="1:11" ht="125.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>12</v>
@@ -928,31 +943,31 @@
     </row>
     <row r="8" spans="1:11" ht="125.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>32</v>
@@ -963,10 +978,10 @@
     </row>
     <row r="9" spans="1:11" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>11</v>
@@ -975,19 +990,19 @@
         <v>37</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>12</v>
@@ -998,10 +1013,10 @@
     </row>
     <row r="10" spans="1:11" ht="102.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>11</v>
@@ -1010,19 +1025,19 @@
         <v>37</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>12</v>
@@ -1033,31 +1048,31 @@
     </row>
     <row r="11" spans="1:11" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>12</v>
@@ -1066,38 +1081,73 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="57" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="57" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>13</v>
       </c>
     </row>
